--- a/KURIKULUM2026_REVISI/043_MATRIKS_CPL_CPMK_BoK_BOUNDARY_GUARDRAILS_PER_SEMESTER-BACKUP.xlsx
+++ b/KURIKULUM2026_REVISI/043_MATRIKS_CPL_CPMK_BoK_BOUNDARY_GUARDRAILS_PER_SEMESTER-BACKUP.xlsx
@@ -3787,7 +3787,7 @@
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>ML statistik / neural network / deep learning (STI-413/STI-626); agen otonom &amp; MAS (STA-602).</t>
+          <t>ML statistik / neural network / deep learning (STI-413/STI-726); agen otonom &amp; MAS (STA-602).</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="B404" s="8" t="inlineStr">
         <is>
-          <t>PyTorch/TensorFlow, CNN/RNN, deep learning (STI-626); sistem otonom BDI &amp; teori permainan (STA-602).</t>
+          <t>PyTorch/TensorFlow, CNN/RNN, deep learning (STI-726); sistem otonom BDI &amp; teori permainan (STA-602).</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="B405" s="7" t="inlineStr">
         <is>
-          <t>Pemodelan data tabular klasik; menyerahkan data tak terstruktur (citra/sekuensial) ke STI-626.</t>
+          <t>Pemodelan data tabular klasik; menyerahkan data tak terstruktur (citra/sekuensial) ke STI-726.</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="B500" s="8" t="inlineStr">
         <is>
-          <t>Layout CSS/HTML (STI-311); message broker skala besar (STI-627); frontend mobile (STI-522).</t>
+          <t>Layout CSS/HTML (STI-311); message broker skala besar (STI-727); frontend mobile (STI-522).</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="B501" s="7" t="inlineStr">
         <is>
-          <t>Layanan backend modular; menyerahkan aksesibilitas mobile ke STI-522 dan skalabilitas terdistribusi ke STI-627.</t>
+          <t>Layanan backend modular; menyerahkan aksesibilitas mobile ke STI-522 dan skalabilitas terdistribusi ke STI-727.</t>
         </is>
       </c>
     </row>
@@ -11223,7 +11223,7 @@
     <row r="721" ht="20" customHeight="1">
       <c r="A721" s="3" t="inlineStr">
         <is>
-          <t>24. STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>24. STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B721" s="4" t="n"/>
@@ -11308,7 +11308,7 @@
     <row r="729" ht="20" customHeight="1">
       <c r="A729" s="3" t="inlineStr">
         <is>
-          <t>24. STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>24. STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B729" s="4" t="n"/>
@@ -11431,7 +11431,7 @@
     <row r="736" ht="20" customHeight="1">
       <c r="A736" s="3" t="inlineStr">
         <is>
-          <t>24. STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>24. STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B736" s="4" t="n"/>
@@ -11642,7 +11642,7 @@
     <row r="747" ht="20" customHeight="1">
       <c r="A747" s="3" t="inlineStr">
         <is>
-          <t>24. STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>24. STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B747" s="4" t="n"/>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="B750" s="8" t="inlineStr">
         <is>
-          <t>Riset/training arsitektur deep learning dari nol (STI-626); pengaturan lifecycle MLOps penuh &amp; CI/CD/CT (STA-701).</t>
+          <t>Riset/training arsitektur deep learning dari nol (STI-726); pengaturan lifecycle MLOps penuh &amp; CI/CD/CT (STA-701).</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11703,7 @@
     <row r="753" ht="20" customHeight="1">
       <c r="A753" s="3" t="inlineStr">
         <is>
-          <t>25. STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>25. STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B753" s="4" t="n"/>
@@ -11788,7 +11788,7 @@
     <row r="761" ht="20" customHeight="1">
       <c r="A761" s="3" t="inlineStr">
         <is>
-          <t>25. STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>25. STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B761" s="4" t="n"/>
@@ -11911,7 +11911,7 @@
     <row r="768" ht="20" customHeight="1">
       <c r="A768" s="3" t="inlineStr">
         <is>
-          <t>25. STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>25. STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B768" s="4" t="n"/>
@@ -12122,7 +12122,7 @@
     <row r="779" ht="20" customHeight="1">
       <c r="A779" s="3" t="inlineStr">
         <is>
-          <t>25. STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>25. STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B779" s="4" t="n"/>
@@ -12183,7 +12183,7 @@
     <row r="785" ht="20" customHeight="1">
       <c r="A785" s="3" t="inlineStr">
         <is>
-          <t>26. STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>26. STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B785" s="4" t="n"/>
@@ -12268,7 +12268,7 @@
     <row r="793" ht="20" customHeight="1">
       <c r="A793" s="3" t="inlineStr">
         <is>
-          <t>26. STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>26. STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B793" s="4" t="n"/>
@@ -12391,7 +12391,7 @@
     <row r="800" ht="20" customHeight="1">
       <c r="A800" s="3" t="inlineStr">
         <is>
-          <t>26. STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>26. STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B800" s="4" t="n"/>
@@ -12602,7 +12602,7 @@
     <row r="811" ht="20" customHeight="1">
       <c r="A811" s="3" t="inlineStr">
         <is>
-          <t>26. STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>26. STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B811" s="4" t="n"/>
@@ -12663,7 +12663,7 @@
     <row r="817" ht="20" customHeight="1">
       <c r="A817" s="3" t="inlineStr">
         <is>
-          <t>27. STI-627 — Digital Platform Engineering</t>
+          <t>27. STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B817" s="4" t="n"/>
@@ -12748,7 +12748,7 @@
     <row r="825" ht="20" customHeight="1">
       <c r="A825" s="3" t="inlineStr">
         <is>
-          <t>27. STI-627 — Digital Platform Engineering</t>
+          <t>27. STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B825" s="4" t="n"/>
@@ -12871,7 +12871,7 @@
     <row r="832" ht="20" customHeight="1">
       <c r="A832" s="3" t="inlineStr">
         <is>
-          <t>27. STI-627 — Digital Platform Engineering</t>
+          <t>27. STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B832" s="4" t="n"/>
@@ -13082,7 +13082,7 @@
     <row r="843" ht="20" customHeight="1">
       <c r="A843" s="3" t="inlineStr">
         <is>
-          <t>27. STI-627 — Digital Platform Engineering</t>
+          <t>27. STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B843" s="4" t="n"/>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="B853" s="7" t="inlineStr">
         <is>
-          <t>STI-627, MKU-204</t>
+          <t>STI-727, MKU-204</t>
         </is>
       </c>
     </row>
@@ -13603,7 +13603,7 @@
       </c>
       <c r="B878" s="8" t="inlineStr">
         <is>
-          <t>Implementasi teknis deep learning/MVP rekayasa (STI-626/STI-627); desain UI (STI-308).</t>
+          <t>Implementasi teknis deep learning/MVP rekayasa (STI-726/STI-727); desain UI (STI-308).</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="B997" s="8" t="inlineStr">
         <is>
-          <t>Menghitung limit/turunan murni manual tanpa kode (STI-102); melatih jaringan deep (STI-626).</t>
+          <t>Menghitung limit/turunan murni manual tanpa kode (STI-102); melatih jaringan deep (STI-726).</t>
         </is>
       </c>
     </row>
@@ -15337,7 +15337,7 @@
       </c>
       <c r="B998" s="7" t="inlineStr">
         <is>
-          <t>Algoritma aproksimasi &amp; optimasi numerik; menyerahkan pemodelan deep learning ke STI-626.</t>
+          <t>Algoritma aproksimasi &amp; optimasi numerik; menyerahkan pemodelan deep learning ke STI-726.</t>
         </is>
       </c>
     </row>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="B1029" s="8" t="inlineStr">
         <is>
-          <t>Inferensi sistem pakar rule-based (STI-307); training deep reinforcement learning skala besar (STI-626).</t>
+          <t>Inferensi sistem pakar rule-based (STI-307); training deep reinforcement learning skala besar (STI-726).</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="B1030" s="7" t="inlineStr">
         <is>
-          <t>Agen otonom terdistribusi; menyerahkan NN besar ke STI-626 dan pengambilan keputusan tunggal ke STI-307.</t>
+          <t>Agen otonom terdistribusi; menyerahkan NN besar ke STI-726 dan pengambilan keputusan tunggal ke STI-307.</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="B1058" s="8" t="inlineStr">
         <is>
-          <t>Provisi VM &amp; kontainer Docker tunggal (STI-417); arsitektur aplikasi microservices (STI-627).</t>
+          <t>Provisi VM &amp; kontainer Docker tunggal (STI-417); arsitektur aplikasi microservices (STI-727).</t>
         </is>
       </c>
     </row>
@@ -16231,7 +16231,7 @@
       </c>
       <c r="B1059" s="7" t="inlineStr">
         <is>
-          <t>Automasi &amp; orkestrasi infrastruktur; menyerahkan desain aplikasi microservices ke STI-627.</t>
+          <t>Automasi &amp; orkestrasi infrastruktur; menyerahkan desain aplikasi microservices ke STI-727.</t>
         </is>
       </c>
     </row>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="B1146" s="7" t="inlineStr">
         <is>
-          <t>Spesialisasi domain vertikal; menyerahkan infrastruktur platform umum ke STI-627/STC-702.</t>
+          <t>Spesialisasi domain vertikal; menyerahkan infrastruktur platform umum ke STI-727/STC-702.</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="B1152" s="7" t="inlineStr">
         <is>
-          <t>STI-413, STI-624</t>
+          <t>STI-413, STI-726</t>
         </is>
       </c>
     </row>
@@ -17875,7 +17875,7 @@
       </c>
       <c r="B1174" s="8" t="inlineStr">
         <is>
-          <t>Riset/training arsitektur model baru (STI-626); deployment layanan inference via FastAPI/ONNX mendalam (STI-624).</t>
+          <t>Riset/training arsitektur model baru (STI-726); deployment layanan inference via FastAPI/ONNX mendalam (STI-726).</t>
         </is>
       </c>
     </row>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="B1175" s="7" t="inlineStr">
         <is>
-          <t>Otomasi &amp; tata kelola model produksi; menyerahkan pembuatan layanan inference ke STI-624.</t>
+          <t>Otomasi &amp; tata kelola model produksi; menyerahkan pembuatan layanan inference ke STI-726.</t>
         </is>
       </c>
     </row>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="B1206" s="8" t="inlineStr">
         <is>
-          <t>Analisis NLP statistik klasik VSM (STI-414); layanan API web kembali (STI-416/STI-624).</t>
+          <t>Analisis NLP statistik klasik VSM (STI-414); layanan API web kembali (STI-416/STI-726).</t>
         </is>
       </c>
     </row>
@@ -18428,7 +18428,7 @@
       </c>
       <c r="B1213" s="7" t="inlineStr">
         <is>
-          <t>STI-626, STI-521</t>
+          <t>STI-726, STI-521</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="B1325" s="8" t="inlineStr">
         <is>
-          <t>Blueprint SPBE selesai; fokus pada proyek bisnis sistem informasi (STI-625); pemodelan UML detail (STI-306).</t>
+          <t>Blueprint SPBE selesai; fokus pada proyek bisnis sistem informasi (STI-727); pemodelan UML detail (STI-306).</t>
         </is>
       </c>
     </row>
@@ -20089,7 +20089,7 @@
       </c>
       <c r="B1326" s="7" t="inlineStr">
         <is>
-          <t>Peta arsitektur enterprise korporat; menyerahkan sistem domain publik ke STI-625.</t>
+          <t>Peta arsitektur enterprise korporat; menyerahkan sistem domain publik ke STI-727.</t>
         </is>
       </c>
     </row>
@@ -20905,7 +20905,7 @@
       </c>
       <c r="B1383" s="8" t="inlineStr">
         <is>
-          <t>Membangun microservice event-driven skalabel (STI-627); penyusunan PRD &amp; metrik produk (STC-703).</t>
+          <t>Membangun microservice event-driven skalabel (STI-727); penyusunan PRD &amp; metrik produk (STC-703).</t>
         </is>
       </c>
     </row>
